--- a/xls/新增 Microsoft Excel 工作表.xlsx
+++ b/xls/新增 Microsoft Excel 工作表.xlsx
@@ -4,15 +4,152 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11865"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="19200" windowHeight="11868"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="124519"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>偷竊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>類別</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>突刺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>治療</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球術</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剝皮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回復術</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>強化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開鎖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰箭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒霧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劍技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解毒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lockpicking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skinning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thrust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poison Cloud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice Bolt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antidote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>General</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Swordsmanship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire Magic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poison Magic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice Magic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,9 +491,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
@@ -366,7 +641,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -377,7 +652,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
